--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>136595648</v>
       </c>
       <c r="B35" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>136595650</v>
       </c>
       <c r="B36" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49702-2023 artfynd.xlsx
+++ b/artfynd/A 49702-2023 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>136595649</v>
       </c>
       <c r="B21" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>136595648</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>136595650</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
